--- a/src/New-release/Contribution to OPH.xlsx
+++ b/src/New-release/Contribution to OPH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officenationalstatistics.sharepoint.com/sites/msdfp/fp/FLOVERVIEW/Floverview + LCLI 2025 IndQ1 - 2025 WEQ2/Figures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livemanchesterac-my.sharepoint.com/personal/nathan_mckeogh_manchester_ac_uk/Documents/Documents/GitHub Repos/TPI-quarterly-data-tool/src/New-release/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6" documentId="11_5243AF8C0829B8832CD2F53CDADF57DB061F2031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43D2C6F7-1CAE-41AA-B980-B61C878563EB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data for Dataviz" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,19 +536,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -557,28 +557,28 @@
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -586,7 +586,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -597,7 +597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -608,7 +608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -619,7 +619,7 @@
         <v>6.9003201E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -630,7 +630,7 @@
         <v>6.8623112999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -641,7 +641,7 @@
         <v>0.10840704299999999</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -652,7 +652,7 @@
         <v>8.2918584000000004E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -663,7 +663,7 @@
         <v>5.6846478999999998E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -674,7 +674,7 @@
         <v>6.3775208999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -685,7 +685,7 @@
         <v>7.452246E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -696,7 +696,7 @@
         <v>0.112765633</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -707,7 +707,7 @@
         <v>4.4668243000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -718,7 +718,7 @@
         <v>1.3556811E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -729,7 +729,7 @@
         <v>2.1315774999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -740,7 +740,7 @@
         <v>5.4132358999999998E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -751,7 +751,7 @@
         <v>1.6491039999999998E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -762,7 +762,7 @@
         <v>1.1606726E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -773,7 +773,7 @@
         <v>1.6656535E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -784,7 +784,7 @@
         <v>3.3096270999999997E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -795,7 +795,7 @@
         <v>9.0201474000000004E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -806,7 +806,7 @@
         <v>4.3743677000000002E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -817,7 +817,7 @@
         <v>8.4739581999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -831,26 +831,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8a54c791-04d1-4dd7-97a3-a882d4048403">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0CEF6E26CBF2C4F8000DAAA032CD586" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4b00db03ba10acd9ce0de4b8508f462a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8a54c791-04d1-4dd7-97a3-a882d4048403" xmlns:ns3="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="93f033296de2705646020d6024e1f2eb" ns2:_="" ns3:_="">
     <xsd:import namespace="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
@@ -1099,14 +1079,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8a54c791-04d1-4dd7-97a3-a882d4048403">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8557CAEA-ABFE-4BAB-A82C-A482A20DAFD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213D9663-DD5E-4730-B7BA-C70A77580769}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
+    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDAD2DC3-87EC-4167-B2AD-C5DBB7ECB4E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDAD2DC3-87EC-4167-B2AD-C5DBB7ECB4E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
+    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213D9663-DD5E-4730-B7BA-C70A77580769}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8557CAEA-ABFE-4BAB-A82C-A482A20DAFD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>